--- a/Violence estimates.xlsx
+++ b/Violence estimates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/vl22683_bristol_ac_uk/Documents/Documents/Misc/UNAIDS/FSW/Analysis/Analysis/Structural-Barriers-FSW-Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="551" documentId="8_{AEEE4C1F-92CE-4094-B9C7-1969C8609B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBCDD7D3-F9F4-4C58-806F-EF517414C1F7}"/>
+  <xr:revisionPtr revIDLastSave="553" documentId="8_{AEEE4C1F-92CE-4094-B9C7-1969C8609B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEE3F5ED-67F1-4A35-A79E-8D80974C6694}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04E804E8-CF61-42BC-A04D-55E2D33F1781}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04E804E8-CF61-42BC-A04D-55E2D33F1781}"/>
   </bookViews>
   <sheets>
     <sheet name="All studies" sheetId="12" r:id="rId1"/>
@@ -133,7 +133,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -217,13 +217,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -242,6 +242,32 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -265,33 +291,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="0.0%"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -476,10 +476,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D9012D00-32F6-4970-A623-C6AEC64A87A7}" name="Table1" displayName="Table1" ref="A1:O69" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" dataCellStyle="Percent">
   <autoFilter ref="A1:O69" xr:uid="{D9012D00-32F6-4970-A623-C6AEC64A87A7}"/>
@@ -504,12 +500,12 @@
     <tableColumn id="11" xr3:uid="{1B360BE7-D329-4CB4-BE36-AE77D8F44371}" name="upper_ln" dataDxfId="4" dataCellStyle="Percent">
       <calculatedColumnFormula>LN(J2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{B788DE6B-5B28-440C-96DA-91E1AC36CE91}" name="or_95" dataDxfId="3" dataCellStyle="Percent">
-      <calculatedColumnFormula>TEXT(F2,"0.00") &amp; " (" &amp; TEXT(H2,"0.00") &amp; "–" &amp; TEXT(J2,"0.00") &amp; ")"</calculatedColumnFormula>
+    <tableColumn id="12" xr3:uid="{B788DE6B-5B28-440C-96DA-91E1AC36CE91}" name="or_95" dataDxfId="0" dataCellStyle="Percent">
+      <calculatedColumnFormula>TEXT(F2,"0.00") &amp; " (" &amp; TEXT(H2,"0.00") &amp; ", " &amp; TEXT(J2,"0.00") &amp; ")"</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{38118F29-992B-431A-8089-300818351178}" name="i2" dataDxfId="2" dataCellStyle="Percent"/>
-    <tableColumn id="14" xr3:uid="{E626C596-936B-46FD-ADE9-6FBDD07D339D}" name="studies" dataDxfId="1"/>
-    <tableColumn id="15" xr3:uid="{62D2FB13-3C5A-46F5-B258-57D1413A340F}" name="estimates" dataDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{38118F29-992B-431A-8089-300818351178}" name="i2" dataDxfId="3" dataCellStyle="Percent"/>
+    <tableColumn id="14" xr3:uid="{E626C596-936B-46FD-ADE9-6FBDD07D339D}" name="studies" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{62D2FB13-3C5A-46F5-B258-57D1413A340F}" name="estimates" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -931,8 +927,8 @@
         <v>0.29266961396282004</v>
       </c>
       <c r="L2" s="7" t="str">
-        <f t="shared" ref="L2:L35" si="3">TEXT(F2,"0.00") &amp; " (" &amp; TEXT(H2,"0.00") &amp; "–" &amp; TEXT(J2,"0.00") &amp; ")"</f>
-        <v>1.15 (0.99–1.34)</v>
+        <f t="shared" ref="L2:L33" si="3">TEXT(F2,"0.00") &amp; " (" &amp; TEXT(H2,"0.00") &amp; ", " &amp; TEXT(J2,"0.00") &amp; ")"</f>
+        <v>1.15 (0.99, 1.34)</v>
       </c>
       <c r="M2" s="8">
         <v>0.57799999999999996</v>
@@ -986,7 +982,7 @@
       </c>
       <c r="L3" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.64 (1.12–2.40)</v>
+        <v>1.64 (1.12, 2.40)</v>
       </c>
       <c r="M3" s="8">
         <v>0.79200000000000004</v>
@@ -1040,7 +1036,7 @@
       </c>
       <c r="L4" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.19 (0.99–1.42)</v>
+        <v>1.19 (0.99, 1.42)</v>
       </c>
       <c r="M4" s="8">
         <v>0.63500000000000001</v>
@@ -1093,8 +1089,8 @@
         <v>0.72754860727727766</v>
       </c>
       <c r="L5" s="7" t="str">
-        <f>TEXT(F5,"0.00") &amp; " (" &amp; TEXT(H5,"0.00") &amp; "–" &amp; TEXT(J5,"0.00") &amp; ")"</f>
-        <v>1.62 (1.27–2.07)</v>
+        <f t="shared" si="3"/>
+        <v>1.62 (1.27, 2.07)</v>
       </c>
       <c r="M5" s="8">
         <v>0.70599999999999996</v>
@@ -1148,7 +1144,7 @@
       </c>
       <c r="L6" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>2.43 (1.46–4.05)</v>
+        <v>2.43 (1.46, 4.05)</v>
       </c>
       <c r="M6" s="8">
         <v>0.63300000000000001</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="L7" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.55 (1.24–1.94)</v>
+        <v>1.55 (1.24, 1.94)</v>
       </c>
       <c r="M7" s="8">
         <v>0.68799999999999994</v>
@@ -1256,7 +1252,7 @@
       </c>
       <c r="L8" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.21 (0.96–1.51)</v>
+        <v>1.21 (0.96, 1.51)</v>
       </c>
       <c r="M8" s="8">
         <v>0.65200000000000002</v>
@@ -1310,7 +1306,7 @@
       </c>
       <c r="L9" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.42 (1.10–1.83)</v>
+        <v>1.42 (1.10, 1.83)</v>
       </c>
       <c r="M9" s="8">
         <v>0.61199999999999999</v>
@@ -1364,7 +1360,7 @@
       </c>
       <c r="L10" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.26 (1.06–1.50)</v>
+        <v>1.26 (1.06, 1.50)</v>
       </c>
       <c r="M10" s="8">
         <v>0.55600000000000005</v>
@@ -1418,7 +1414,7 @@
       </c>
       <c r="L11" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.17 (0.78–1.75)</v>
+        <v>1.17 (0.78, 1.75)</v>
       </c>
       <c r="M11" s="8">
         <v>0.61699999999999999</v>
@@ -1472,7 +1468,7 @@
       </c>
       <c r="L12" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.36 (0.98–1.87)</v>
+        <v>1.36 (0.98, 1.87)</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
@@ -1526,7 +1522,7 @@
       </c>
       <c r="L13" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.15 (0.77–1.71)</v>
+        <v>1.15 (0.77, 1.71)</v>
       </c>
       <c r="M13" s="8">
         <v>0.59099999999999997</v>
@@ -1580,7 +1576,7 @@
       </c>
       <c r="L14" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.32 (1.16–1.50)</v>
+        <v>1.32 (1.16, 1.50)</v>
       </c>
       <c r="M14" s="8">
         <v>0.65200000000000002</v>
@@ -1634,7 +1630,7 @@
       </c>
       <c r="L15" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.60 (1.33–1.92)</v>
+        <v>1.60 (1.33, 1.92)</v>
       </c>
       <c r="M15" s="8">
         <v>0.68400000000000005</v>
@@ -1688,7 +1684,7 @@
       </c>
       <c r="L16" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.31 (1.16–1.48)</v>
+        <v>1.31 (1.16, 1.48)</v>
       </c>
       <c r="M16" s="8">
         <v>0.63400000000000001</v>
@@ -1742,7 +1738,7 @@
       </c>
       <c r="L17" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.42 (1.19–1.70)</v>
+        <v>1.42 (1.19, 1.70)</v>
       </c>
       <c r="M17" s="8">
         <v>0.32900000000000001</v>
@@ -1793,7 +1789,7 @@
       </c>
       <c r="L18" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.32 (1.15–1.52)</v>
+        <v>1.32 (1.15, 1.52)</v>
       </c>
       <c r="M18" s="8">
         <v>0.36099999999999999</v>
@@ -1844,7 +1840,7 @@
       </c>
       <c r="L19" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.29 (1.15–1.44)</v>
+        <v>1.29 (1.15, 1.44)</v>
       </c>
       <c r="M19" s="8">
         <v>0</v>
@@ -1894,8 +1890,8 @@
         <v>0.58778666490211906</v>
       </c>
       <c r="L20" s="7" t="str">
-        <f>TEXT(F20,"0.00") &amp; " (" &amp; TEXT(H20,"0.00") &amp; "–" &amp; TEXT(J20,"0.00") &amp; ")"</f>
-        <v>1.49 (1.23–1.80)</v>
+        <f t="shared" si="3"/>
+        <v>1.49 (1.23, 1.80)</v>
       </c>
       <c r="M20" s="8">
         <v>0.78900000000000003</v>
@@ -1946,7 +1942,7 @@
       </c>
       <c r="L21" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.57 (1.27–1.93)</v>
+        <v>1.57 (1.27, 1.93)</v>
       </c>
       <c r="M21" s="8">
         <v>0.40200000000000002</v>
@@ -1997,7 +1993,7 @@
       </c>
       <c r="L22" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.40 (1.21–1.63)</v>
+        <v>1.40 (1.21, 1.63)</v>
       </c>
       <c r="M22" s="8">
         <v>0.47199999999999998</v>
@@ -2048,7 +2044,7 @@
       </c>
       <c r="L23" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.34 (1.10–1.62)</v>
+        <v>1.34 (1.10, 1.62)</v>
       </c>
       <c r="M23" s="8">
         <v>0.68</v>
@@ -2099,7 +2095,7 @@
       </c>
       <c r="L24" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.38 (1.24–1.55)</v>
+        <v>1.38 (1.24, 1.55)</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
@@ -2150,7 +2146,7 @@
       </c>
       <c r="L25" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.29 (1.13–1.48)</v>
+        <v>1.29 (1.13, 1.48)</v>
       </c>
       <c r="M25" s="8">
         <v>0.56599999999999995</v>
@@ -2201,7 +2197,7 @@
       </c>
       <c r="L26" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.42 (1.27–1.59)</v>
+        <v>1.42 (1.27, 1.59)</v>
       </c>
       <c r="M26" s="8">
         <v>0.68200000000000005</v>
@@ -2252,7 +2248,7 @@
       </c>
       <c r="L27" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.51 (1.31–1.74)</v>
+        <v>1.51 (1.31, 1.74)</v>
       </c>
       <c r="M27" s="8">
         <v>0.27300000000000002</v>
@@ -2303,7 +2299,7 @@
       </c>
       <c r="L28" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.35 (1.23–1.48)</v>
+        <v>1.35 (1.23, 1.48)</v>
       </c>
       <c r="M28" s="8">
         <v>0.39100000000000001</v>
@@ -2354,7 +2350,7 @@
       </c>
       <c r="L29" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.25 (0.92–1.69)</v>
+        <v>1.25 (0.92, 1.69)</v>
       </c>
       <c r="M29" s="8">
         <v>0.82</v>
@@ -2405,7 +2401,7 @@
       </c>
       <c r="L30" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>0.98 (0.83–1.17)</v>
+        <v>0.98 (0.83, 1.17)</v>
       </c>
       <c r="M30" s="8">
         <v>0.41699999999999998</v>
@@ -2456,7 +2452,7 @@
       </c>
       <c r="L31" s="7" t="str">
         <f t="shared" si="3"/>
-        <v>1.11 (0.86–1.45)</v>
+        <v>1.11 (0.86, 1.45)</v>
       </c>
       <c r="M31" s="8">
         <v>0.78700000000000003</v>
@@ -2506,8 +2502,8 @@
         <v>0.83724752453370221</v>
       </c>
       <c r="L32" s="7" t="str">
-        <f>TEXT(F32,"0.00") &amp; " (" &amp; TEXT(H32,"0.00") &amp; "–" &amp; TEXT(J32,"0.00") &amp; ")"</f>
-        <v>1.40 (0.85–2.31)</v>
+        <f t="shared" si="3"/>
+        <v>1.40 (0.85, 2.31)</v>
       </c>
       <c r="M32" s="8">
         <v>0.872</v>
@@ -2557,8 +2553,8 @@
         <v>0.35767444427181588</v>
       </c>
       <c r="L33" s="7" t="str">
-        <f>TEXT(F33,"0.00") &amp; " (" &amp; TEXT(H33,"0.00") &amp; "–" &amp; TEXT(J33,"0.00") &amp; ")"</f>
-        <v>1.10 (0.84–1.43)</v>
+        <f t="shared" si="3"/>
+        <v>1.10 (0.84, 1.43)</v>
       </c>
       <c r="M33" s="8">
         <v>0.70799999999999996</v>
@@ -2608,8 +2604,8 @@
         <v>0.3148107398400336</v>
       </c>
       <c r="L34" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>1.06 (0.82–1.37)</v>
+        <f t="shared" ref="L34:L69" si="4">TEXT(F34,"0.00") &amp; " (" &amp; TEXT(H34,"0.00") &amp; ", " &amp; TEXT(J34,"0.00") &amp; ")"</f>
+        <v>1.06 (0.82, 1.37)</v>
       </c>
       <c r="M34" s="8">
         <v>0.65400000000000003</v>
@@ -2659,8 +2655,8 @@
         <v>0.17395330712343798</v>
       </c>
       <c r="L35" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>0.98 (0.81–1.19)</v>
+        <f t="shared" si="4"/>
+        <v>0.98 (0.81, 1.19)</v>
       </c>
       <c r="M35" s="8">
         <v>0.56100000000000005</v>
@@ -2692,26 +2688,26 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G36" s="7">
-        <f t="shared" ref="G36:G69" si="4">LN(F36)</f>
+        <f t="shared" ref="G36:G69" si="5">LN(F36)</f>
         <v>9.5310179804324935E-2</v>
       </c>
       <c r="H36" s="3">
         <v>0.87</v>
       </c>
       <c r="I36" s="7">
-        <f t="shared" ref="I36:I69" si="5">LN(H36)</f>
+        <f t="shared" ref="I36:I69" si="6">LN(H36)</f>
         <v>-0.13926206733350766</v>
       </c>
       <c r="J36" s="3">
         <v>1.39</v>
       </c>
       <c r="K36" s="7">
-        <f t="shared" ref="K36:K69" si="6">LN(J36)</f>
+        <f t="shared" ref="K36:K69" si="7">LN(J36)</f>
         <v>0.3293037471426003</v>
       </c>
       <c r="L36" s="7" t="str">
-        <f t="shared" ref="L36:L69" si="7">TEXT(F36,"0.00") &amp; " (" &amp; TEXT(H36,"0.00") &amp; "–" &amp; TEXT(J36,"0.00") &amp; ")"</f>
-        <v>1.10 (0.87–1.39)</v>
+        <f t="shared" si="4"/>
+        <v>1.10 (0.87, 1.39)</v>
       </c>
       <c r="M36" s="8">
         <v>0.63400000000000001</v>
@@ -2761,8 +2757,8 @@
         <v>-2.0202707317519466E-2</v>
       </c>
       <c r="L37" s="7" t="str">
-        <f>TEXT(F37,"0.00") &amp; " (" &amp; TEXT(H37,"0.00") &amp; "–" &amp; TEXT(J37,"0.00") &amp; ")"</f>
-        <v>0.87 (0.77–0.98)</v>
+        <f t="shared" si="4"/>
+        <v>0.87 (0.77, 0.98)</v>
       </c>
       <c r="M37" s="8">
         <v>0</v>
@@ -2812,8 +2808,8 @@
         <v>-1.0050335853501451E-2</v>
       </c>
       <c r="L38" s="7" t="str">
-        <f>TEXT(F38,"0.00") &amp; " (" &amp; TEXT(H38,"0.00") &amp; "–" &amp; TEXT(J38,"0.00") &amp; ")"</f>
-        <v>0.87 (0.77–0.99)</v>
+        <f t="shared" si="4"/>
+        <v>0.87 (0.77, 0.99)</v>
       </c>
       <c r="M38" s="8">
         <v>0</v>
@@ -2863,8 +2859,8 @@
         <v>0.10436001532424286</v>
       </c>
       <c r="L39" s="7" t="str">
-        <f>TEXT(F39,"0.00") &amp; " (" &amp; TEXT(H39,"0.00") &amp; "–" &amp; TEXT(J39,"0.00") &amp; ")"</f>
-        <v>0.85 (0.66–1.11)</v>
+        <f t="shared" si="4"/>
+        <v>0.85 (0.66, 1.11)</v>
       </c>
       <c r="M39" s="8">
         <v>0.78</v>
@@ -2914,8 +2910,8 @@
         <v>6.7658648473814864E-2</v>
       </c>
       <c r="L40" s="7" t="str">
-        <f>TEXT(F40,"0.00") &amp; " (" &amp; TEXT(H40,"0.00") &amp; "–" &amp; TEXT(J40,"0.00") &amp; ")"</f>
-        <v>0.84 (0.67–1.07)</v>
+        <f t="shared" si="4"/>
+        <v>0.84 (0.67, 1.07)</v>
       </c>
       <c r="M40" s="8">
         <v>0.71099999999999997</v>
@@ -2947,26 +2943,26 @@
         <v>1.01</v>
       </c>
       <c r="G41" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.950330853168092E-3</v>
       </c>
       <c r="H41" s="3">
         <v>0.68</v>
       </c>
       <c r="I41" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.38566248081198462</v>
       </c>
       <c r="J41" s="3">
         <v>1.51</v>
       </c>
       <c r="K41" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.41210965082683298</v>
       </c>
       <c r="L41" s="7" t="str">
-        <f t="shared" ref="L41" si="8">TEXT(F41,"0.00") &amp; " (" &amp; TEXT(H41,"0.00") &amp; "–" &amp; TEXT(J41,"0.00") &amp; ")"</f>
-        <v>1.01 (0.68–1.51)</v>
+        <f t="shared" si="4"/>
+        <v>1.01 (0.68, 1.51)</v>
       </c>
       <c r="M41" s="8">
         <v>0.80600000000000005</v>
@@ -2998,26 +2994,26 @@
         <v>0.97</v>
       </c>
       <c r="G42" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.0459207484708574E-2</v>
       </c>
       <c r="H42" s="3">
         <v>0.75</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.2876820724517809</v>
       </c>
       <c r="J42" s="3">
         <v>1.25</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.22314355131420976</v>
       </c>
       <c r="L42" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.97 (0.75–1.25)</v>
+        <f t="shared" si="4"/>
+        <v>0.97 (0.75, 1.25)</v>
       </c>
       <c r="M42" s="8">
         <v>0.69499999999999995</v>
@@ -3067,8 +3063,8 @@
         <v>0.39877611995736778</v>
       </c>
       <c r="L43" s="7" t="str">
-        <f>TEXT(F43,"0.00") &amp; " (" &amp; TEXT(H43,"0.00") &amp; "–" &amp; TEXT(J43,"0.00") &amp; ")"</f>
-        <v>1.10 (0.81–1.49)</v>
+        <f t="shared" si="4"/>
+        <v>1.10 (0.81, 1.49)</v>
       </c>
       <c r="M43" s="8">
         <v>0.77500000000000002</v>
@@ -3100,26 +3096,26 @@
         <v>0.82</v>
       </c>
       <c r="G44" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.19845093872383832</v>
       </c>
       <c r="H44" s="7">
         <v>0.68</v>
       </c>
       <c r="I44" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.38566248081198462</v>
       </c>
       <c r="J44" s="7">
         <v>0.99</v>
       </c>
       <c r="K44" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.0050335853501451E-2</v>
       </c>
       <c r="L44" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.82 (0.68–0.99)</v>
+        <f t="shared" si="4"/>
+        <v>0.82 (0.68, 0.99)</v>
       </c>
       <c r="M44" s="8">
         <v>0</v>
@@ -3151,26 +3147,26 @@
         <v>0.78</v>
       </c>
       <c r="G45" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.24846135929849961</v>
       </c>
       <c r="H45" s="7">
         <v>0.56000000000000005</v>
       </c>
       <c r="I45" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.57981849525294205</v>
       </c>
       <c r="J45" s="7">
         <v>1.08</v>
       </c>
       <c r="K45" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.6961041136128394E-2</v>
       </c>
       <c r="L45" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.78 (0.56–1.08)</v>
+        <f t="shared" si="4"/>
+        <v>0.78 (0.56, 1.08)</v>
       </c>
       <c r="M45" s="8">
         <v>0.49</v>
@@ -3202,26 +3198,26 @@
         <v>0.78</v>
       </c>
       <c r="G46" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.24846135929849961</v>
       </c>
       <c r="H46" s="3">
         <v>0.64</v>
       </c>
       <c r="I46" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.44628710262841947</v>
       </c>
       <c r="J46" s="3">
         <v>0.94</v>
       </c>
       <c r="K46" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-6.1875403718087529E-2</v>
       </c>
       <c r="L46" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.78 (0.64–0.94)</v>
+        <f t="shared" si="4"/>
+        <v>0.78 (0.64, 0.94)</v>
       </c>
       <c r="M46" s="8">
         <v>8.5000000000000006E-2</v>
@@ -3271,8 +3267,8 @@
         <v>0.33647223662121289</v>
       </c>
       <c r="L47" s="7" t="str">
-        <f>TEXT(F47,"0.00") &amp; " (" &amp; TEXT(H47,"0.00") &amp; "–" &amp; TEXT(J47,"0.00") &amp; ")"</f>
-        <v>0.72 (0.38–1.40)</v>
+        <f t="shared" si="4"/>
+        <v>0.72 (0.38, 1.40)</v>
       </c>
       <c r="M47" s="8">
         <v>0</v>
@@ -3322,8 +3318,8 @@
         <v>0.37156355643248301</v>
       </c>
       <c r="L48" s="7" t="str">
-        <f>TEXT(F48,"0.00") &amp; " (" &amp; TEXT(H48,"0.00") &amp; "–" &amp; TEXT(J48,"0.00") &amp; ")"</f>
-        <v>0.71 (0.35–1.45)</v>
+        <f t="shared" si="4"/>
+        <v>0.71 (0.35, 1.45)</v>
       </c>
       <c r="M48" s="8">
         <v>0</v>
@@ -3373,8 +3369,8 @@
         <v>4.8790164169432049E-2</v>
       </c>
       <c r="L49" s="7" t="str">
-        <f>TEXT(F49,"0.00") &amp; " (" &amp; TEXT(H49,"0.00") &amp; "–" &amp; TEXT(J49,"0.00") &amp; ")"</f>
-        <v>0.83 (0.66–1.05)</v>
+        <f t="shared" si="4"/>
+        <v>0.83 (0.66, 1.05)</v>
       </c>
       <c r="M49" s="8">
         <v>0</v>
@@ -3406,26 +3402,26 @@
         <v>0.72</v>
       </c>
       <c r="G50" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.3285040669720361</v>
       </c>
       <c r="H50" s="3">
         <v>0.57999999999999996</v>
       </c>
       <c r="I50" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.54472717544167215</v>
       </c>
       <c r="J50" s="3">
         <v>0.91</v>
       </c>
       <c r="K50" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-9.431067947124129E-2</v>
       </c>
       <c r="L50" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.72 (0.58–0.91)</v>
+        <f t="shared" si="4"/>
+        <v>0.72 (0.58, 0.91)</v>
       </c>
       <c r="M50" s="8">
         <v>0</v>
@@ -3457,26 +3453,26 @@
         <v>0.66</v>
       </c>
       <c r="G51" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.41551544396166579</v>
       </c>
       <c r="H51" s="3">
         <v>0.46</v>
       </c>
       <c r="I51" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.77652878949899629</v>
       </c>
       <c r="J51" s="3">
         <v>0.96</v>
       </c>
       <c r="K51" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-4.0821994520255166E-2</v>
       </c>
       <c r="L51" s="7" t="str">
-        <f t="shared" ref="L51:L52" si="9">TEXT(F51,"0.00") &amp; " (" &amp; TEXT(H51,"0.00") &amp; "–" &amp; TEXT(J51,"0.00") &amp; ")"</f>
-        <v>0.66 (0.46–0.96)</v>
+        <f t="shared" si="4"/>
+        <v>0.66 (0.46, 0.96)</v>
       </c>
       <c r="M51" s="8">
         <v>0.50600000000000001</v>
@@ -3508,26 +3504,26 @@
         <v>0.68</v>
       </c>
       <c r="G52" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.38566248081198462</v>
       </c>
       <c r="H52" s="3">
         <v>0.54</v>
       </c>
       <c r="I52" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.61618613942381695</v>
       </c>
       <c r="J52" s="3">
         <v>0.87</v>
       </c>
       <c r="K52" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-0.13926206733350766</v>
       </c>
       <c r="L52" s="7" t="str">
-        <f t="shared" si="9"/>
-        <v>0.68 (0.54–0.87)</v>
+        <f t="shared" si="4"/>
+        <v>0.68 (0.54, 0.87)</v>
       </c>
       <c r="M52" s="8">
         <v>0</v>
@@ -3559,26 +3555,26 @@
         <v>0.63</v>
       </c>
       <c r="G53" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.46203545959655867</v>
       </c>
       <c r="H53" s="3">
         <v>0.33</v>
       </c>
       <c r="I53" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.1086626245216111</v>
       </c>
       <c r="J53" s="3">
         <v>1.24</v>
       </c>
       <c r="K53" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.21511137961694549</v>
       </c>
       <c r="L53" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>0.63 (0.33–1.24)</v>
+        <f t="shared" si="4"/>
+        <v>0.63 (0.33, 1.24)</v>
       </c>
       <c r="M53" s="8">
         <v>0.70599999999999996</v>
@@ -3610,26 +3606,26 @@
         <v>0.65</v>
       </c>
       <c r="G54" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.43078291609245423</v>
       </c>
       <c r="H54" s="3">
         <v>0.28000000000000003</v>
       </c>
       <c r="I54" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.2729656758128873</v>
       </c>
       <c r="J54" s="3">
         <v>1.49</v>
       </c>
       <c r="K54" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.39877611995736778</v>
       </c>
       <c r="L54" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>0.65 (0.28–1.49)</v>
+        <f t="shared" si="4"/>
+        <v>0.65 (0.28, 1.49)</v>
       </c>
       <c r="M54" s="8">
         <v>0.69799999999999995</v>
@@ -3661,26 +3657,26 @@
         <v>0.65</v>
       </c>
       <c r="G55" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.43078291609245423</v>
       </c>
       <c r="H55" s="3">
         <v>0.33</v>
       </c>
       <c r="I55" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.1086626245216111</v>
       </c>
       <c r="J55" s="3">
         <v>1.29</v>
       </c>
       <c r="K55" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.25464221837358075</v>
       </c>
       <c r="L55" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>0.65 (0.33–1.29)</v>
+        <f t="shared" si="4"/>
+        <v>0.65 (0.33, 1.29)</v>
       </c>
       <c r="M55" s="8">
         <v>0.67500000000000004</v>
@@ -3712,26 +3708,26 @@
         <v>0.5</v>
       </c>
       <c r="G56" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.69314718055994529</v>
       </c>
       <c r="H56" s="3">
         <v>0.33</v>
       </c>
       <c r="I56" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-1.1086626245216111</v>
       </c>
       <c r="J56" s="3">
         <v>0.76</v>
       </c>
       <c r="K56" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-0.2744368457017603</v>
       </c>
       <c r="L56" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>0.50 (0.33–0.76)</v>
+        <f t="shared" si="4"/>
+        <v>0.50 (0.33, 0.76)</v>
       </c>
       <c r="M56" s="8">
         <v>0.74199999999999999</v>
@@ -3781,8 +3777,8 @@
         <v>-0.26136476413440751</v>
       </c>
       <c r="L57" s="9" t="str">
-        <f>TEXT(F57,"0.00") &amp; " (" &amp; TEXT(H57,"0.00") &amp; "–" &amp; TEXT(J57,"0.00") &amp; ")"</f>
-        <v>0.48 (0.30–0.77)</v>
+        <f t="shared" si="4"/>
+        <v>0.48 (0.30, 0.77)</v>
       </c>
       <c r="M57" s="8">
         <v>0.72499999999999998</v>
@@ -3832,8 +3828,8 @@
         <v>-0.26136476413440751</v>
       </c>
       <c r="L58" s="9" t="str">
-        <f>TEXT(F58,"0.00") &amp; " (" &amp; TEXT(H58,"0.00") &amp; "–" &amp; TEXT(J58,"0.00") &amp; ")"</f>
-        <v>0.49 (0.31–0.77)</v>
+        <f t="shared" si="4"/>
+        <v>0.49 (0.31, 0.77)</v>
       </c>
       <c r="M58" s="8">
         <v>0.69399999999999995</v>
@@ -3865,26 +3861,26 @@
         <v>0.9</v>
       </c>
       <c r="G59" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.10536051565782628</v>
       </c>
       <c r="H59" s="7">
         <v>0.69</v>
       </c>
       <c r="I59" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.37106368139083207</v>
       </c>
       <c r="J59" s="7">
         <v>1.19</v>
       </c>
       <c r="K59" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.17395330712343798</v>
       </c>
       <c r="L59" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.90 (0.69–1.19)</v>
+        <f t="shared" si="4"/>
+        <v>0.90 (0.69, 1.19)</v>
       </c>
       <c r="M59" s="8">
         <v>0.252</v>
@@ -3934,8 +3930,8 @@
         <v>0.85441532815606758</v>
       </c>
       <c r="L60" s="7" t="str">
-        <f>TEXT(F60,"0.00") &amp; " (" &amp; TEXT(H60,"0.00") &amp; "–" &amp; TEXT(J60,"0.00") &amp; ")"</f>
-        <v>1.26 (0.67–2.35)</v>
+        <f t="shared" si="4"/>
+        <v>1.26 (0.67, 2.35)</v>
       </c>
       <c r="M60" s="8">
         <v>0.28999999999999998</v>
@@ -3985,8 +3981,8 @@
         <v>0.15700374880966469</v>
       </c>
       <c r="L61" s="7" t="str">
-        <f>TEXT(F61,"0.00") &amp; " (" &amp; TEXT(H61,"0.00") &amp; "–" &amp; TEXT(J61,"0.00") &amp; ")"</f>
-        <v>0.88 (0.67–1.17)</v>
+        <f t="shared" si="4"/>
+        <v>0.88 (0.67, 1.17)</v>
       </c>
       <c r="M61" s="8">
         <v>0.124</v>
@@ -4018,26 +4014,26 @@
         <v>1.18</v>
       </c>
       <c r="G62" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.16551443847757333</v>
       </c>
       <c r="H62" s="3">
         <v>0.51</v>
       </c>
       <c r="I62" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.67334455326376563</v>
       </c>
       <c r="J62" s="3">
         <v>2.72</v>
       </c>
       <c r="K62" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.000631880307906</v>
       </c>
       <c r="L62" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>1.18 (0.51–2.72)</v>
+        <f t="shared" si="4"/>
+        <v>1.18 (0.51, 2.72)</v>
       </c>
       <c r="M62" s="8">
         <v>0.66900000000000004</v>
@@ -4087,8 +4083,8 @@
         <v>1.297463147413275</v>
       </c>
       <c r="L63" s="7" t="str">
-        <f>TEXT(F63,"0.00") &amp; " (" &amp; TEXT(H63,"0.00") &amp; "–" &amp; TEXT(J63,"0.00") &amp; ")"</f>
-        <v>1.57 (0.67–3.66)</v>
+        <f t="shared" si="4"/>
+        <v>1.57 (0.67, 3.66)</v>
       </c>
       <c r="M63" s="8">
         <v>0.61499999999999999</v>
@@ -4138,8 +4134,8 @@
         <v>0.94778939893352609</v>
       </c>
       <c r="L64" s="7" t="str">
-        <f>TEXT(F64,"0.00") &amp; " (" &amp; TEXT(H64,"0.00") &amp; "–" &amp; TEXT(J64,"0.00") &amp; ")"</f>
-        <v>1.15 (0.51–2.58)</v>
+        <f t="shared" si="4"/>
+        <v>1.15 (0.51, 2.58)</v>
       </c>
       <c r="M64" s="8">
         <v>0.61299999999999999</v>
@@ -4171,26 +4167,26 @@
         <v>0.67</v>
       </c>
       <c r="G65" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.40047756659712525</v>
       </c>
       <c r="H65" s="7">
         <v>0.51</v>
       </c>
       <c r="I65" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.67334455326376563</v>
       </c>
       <c r="J65" s="7">
         <v>0.88</v>
       </c>
       <c r="K65" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-0.12783337150988489</v>
       </c>
       <c r="L65" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.67 (0.51–0.88)</v>
+        <f t="shared" si="4"/>
+        <v>0.67 (0.51, 0.88)</v>
       </c>
       <c r="M65" s="8">
         <v>0.114</v>
@@ -4222,26 +4218,26 @@
         <v>0.89</v>
       </c>
       <c r="G66" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.11653381625595151</v>
       </c>
       <c r="H66" s="3">
         <v>0.81</v>
       </c>
       <c r="I66" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.21072103131565253</v>
       </c>
       <c r="J66" s="3">
         <v>0.98</v>
       </c>
       <c r="K66" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.0202707317519466E-2</v>
       </c>
       <c r="L66" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.89 (0.81–0.98)</v>
+        <f t="shared" si="4"/>
+        <v>0.89 (0.81, 0.98)</v>
       </c>
       <c r="M66" s="8">
         <v>0.372</v>
@@ -4273,26 +4269,26 @@
         <v>0.88</v>
       </c>
       <c r="G67" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.12783337150988489</v>
       </c>
       <c r="H67" s="3">
         <v>0.79</v>
       </c>
       <c r="I67" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.23572233352106983</v>
       </c>
       <c r="J67" s="3">
         <v>0.98</v>
       </c>
       <c r="K67" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-2.0202707317519466E-2</v>
       </c>
       <c r="L67" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.88 (0.79–0.98)</v>
+        <f t="shared" si="4"/>
+        <v>0.88 (0.79, 0.98)</v>
       </c>
       <c r="M67" s="8">
         <v>0.20300000000000001</v>
@@ -4340,8 +4336,8 @@
         <v>-0.1743533871447778</v>
       </c>
       <c r="L68" s="7" t="str">
-        <f>TEXT(F68,"0.00") &amp; " (" &amp; TEXT(H68,"0.00") &amp; "–" &amp; TEXT(J68,"0.00") &amp; ")"</f>
-        <v>0.67 (0.54–0.84)</v>
+        <f t="shared" si="4"/>
+        <v>0.67 (0.54, 0.84)</v>
       </c>
       <c r="M68" s="8">
         <v>0.114</v>
@@ -4373,26 +4369,26 @@
         <v>0.72</v>
       </c>
       <c r="G69" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.3285040669720361</v>
       </c>
       <c r="H69" s="3">
         <v>0.49</v>
       </c>
       <c r="I69" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-0.71334988787746478</v>
       </c>
       <c r="J69" s="3">
         <v>1.06</v>
       </c>
       <c r="K69" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.8268908123975824E-2</v>
       </c>
       <c r="L69" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>0.72 (0.49–1.06)</v>
+        <f t="shared" si="4"/>
+        <v>0.72 (0.49, 1.06)</v>
       </c>
       <c r="M69" s="8">
         <v>0.46100000000000002</v>
